--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,69 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4039,8 +4182,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4059,956 +4206,946 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청춘가 — 민요채보-1/청춘가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">청춘가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="20"/>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">덧</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">号</t>
         </is>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="21"/>
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="22"/>
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="22"/>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="K4" s="22"/>
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">号</t>
         </is>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="24"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="K5" s="25"/>
+      <c r="L5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="25"/>
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="Q5" s="25"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="20"/>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="27"/>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">학</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 南</t>
         </is>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="22"/>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="22"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="22"/>
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="Q7" s="22"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 仲</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 無</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="25"/>
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="25"/>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="20"/>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="22"/>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I10" s="22"/>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="22"/>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="22"/>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 㴌</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="22"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="25"/>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="25"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="25"/>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="25"/>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="Q11" s="25"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="27"/>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="22"/>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="22"/>
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="I13" s="22"/>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="22"/>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="22"/>
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="22"/>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="25"/>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="25"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I14" s="25"/>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="25"/>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 南</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="25"/>
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -978,12 +978,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4805,7 +4805,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4839,7 +4839,7 @@
       <c r="I10" s="9"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4850,19 +4850,19 @@
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -5027,7 +5027,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -5095,7 +5095,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -5120,7 +5120,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="10"/>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4234,104 +4275,104 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">청춘가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">덧</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">청춘가</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="O3" s="24"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4339,74 +4380,74 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밭</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">딸</t>
         </is>
@@ -4414,70 +4455,70 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">손</t>
         </is>
@@ -4485,79 +4526,79 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">학</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -4565,152 +4606,152 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="27"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㒇
 南</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">오늘</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">오늘</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4718,84 +4759,84 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -4803,221 +4844,221 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아안</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="O11" s="26"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5025,67 +5066,67 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="27"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5093,59 +5134,59 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -4252,28 +4252,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25"/>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
@@ -4968,7 +4968,7 @@
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="O11" s="26"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="Q11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5064,12 +5064,12 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -5132,12 +5132,12 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -5155,7 +5155,7 @@
       <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="26"/>

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -4356,7 +4356,9 @@
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">청춘가</t>
+          <t xml:space="preserve">청
+춘
+가</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -4720,7 +4722,8 @@
       </c>
       <c r="K8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">오늘</t>
+          <t xml:space="preserve">오
+늘</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -4731,7 +4734,8 @@
       </c>
       <c r="M8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">오늘</t>
+          <t xml:space="preserve">오
+늘</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -4952,7 +4956,8 @@
       </c>
       <c r="K11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">아안</t>
+          <t xml:space="preserve">아
+안</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4304,14 +4327,14 @@
 仲</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
@@ -4322,7 +4345,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">덧</t>
         </is>
@@ -4333,7 +4356,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -4344,7 +4367,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
@@ -4354,7 +4377,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">청
 춘
@@ -4367,14 +4390,14 @@
 汰</t>
         </is>
       </c>
-      <c r="O3" s="24"/>
+      <c r="O3" s="30"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4387,13 +4410,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">밭</t>
         </is>
@@ -4403,7 +4426,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
@@ -4413,7 +4436,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4423,7 +4446,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4433,13 +4456,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4449,7 +4472,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">딸</t>
         </is>
@@ -4462,13 +4485,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4478,7 +4501,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4488,7 +4511,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4498,19 +4521,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4520,7 +4543,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">손</t>
         </is>
@@ -4534,13 +4557,13 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
@@ -4551,7 +4574,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4561,7 +4584,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -4572,14 +4595,14 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="29"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -4590,7 +4613,7 @@
 汰</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">학</t>
         </is>
@@ -4600,7 +4623,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -4614,14 +4637,14 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㒇
 南</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4632,7 +4655,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4642,14 +4665,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4660,7 +4683,7 @@
 南</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4671,7 +4694,7 @@
 汰</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -4681,7 +4704,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4690,14 +4713,14 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4708,19 +4731,19 @@
 無</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 늘</t>
@@ -4732,7 +4755,7 @@
 南</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 늘</t>
@@ -4744,7 +4767,7 @@
 無</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="O8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
@@ -4755,7 +4778,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="Q8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4769,7 +4792,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4779,7 +4802,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4790,7 +4813,7 @@
 無</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4800,7 +4823,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4810,7 +4833,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -4820,7 +4843,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4830,7 +4853,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4840,7 +4863,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -4854,7 +4877,7 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4864,7 +4887,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4874,21 +4897,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
@@ -4898,20 +4921,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4920,7 +4943,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4930,7 +4953,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4941,20 +4964,20 @@
 無</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 안</t>
@@ -4965,7 +4988,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4976,13 +4999,13 @@
 –</t>
         </is>
       </c>
-      <c r="O11" s="26"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="34"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -4991,7 +5014,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5001,7 +5024,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5011,7 +5034,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5022,7 +5045,7 @@
 無</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5032,7 +5055,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -5042,7 +5065,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5052,7 +5075,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -5063,7 +5086,7 @@
 無</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5077,33 +5100,33 @@
 –</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -5114,14 +5137,14 @@
 無</t>
         </is>
       </c>
-      <c r="M13" s="27"/>
+      <c r="M13" s="33"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -5131,7 +5154,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5145,43 +5168,43 @@
 –</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="26" t="inlineStr">
+      <c r="O14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -5191,7 +5214,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="26" t="inlineStr">
+      <c r="Q14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,31 +227,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
     </row>
@@ -389,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -399,7 +376,11 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 18%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -425,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 여백에 세로로 "청춘가 굿거리" 표기. 12정간 양식, 굵은 선 3칸마다. 8줄 모두 사용. 글씨가 빽빽하고 겹쳐 쓴 곳이 많아 일부 율명·가사 불확실. 하단 "- 197 -"은 양식 용지 번호. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 오른쪽 여백에 세로로 "청춘가 굿거리". 가사는 각 율명 줄 오른쪽 칸. 1절(줄1~4) 이팔은 청춘에 소년 몸 되어서 문명의 학문을 닦아 봅시다, 2절(줄5~8) 청춘 홍안을 (네) 자랑 마라 덧없는 세월에 백발이 되누나 — 같은 가락 두 번(줄1~4 ≒ 줄5~8, 청성 위주로 약간 다름). 줄4 정간1~3 가사 칸은 지운 흔적. 南 오른쪽 작은 꺾쇠는 ^.</t>
         </is>
       </c>
     </row>
@@ -663,7 +644,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">딸</t>
+          <t xml:space="preserve">팔</t>
         </is>
       </c>
       <c r="J3" s="4"/>
@@ -690,22 +671,26 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">손</t>
-        </is>
-      </c>
-      <c r="J4" s="4"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 은/는?</t>
+        </is>
+      </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5">
@@ -741,7 +726,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">경</t>
+          <t xml:space="preserve">청</t>
         </is>
       </c>
       <c r="J5" s="4"/>
@@ -843,26 +828,22 @@
       <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰(氵太)</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9">
@@ -888,13 +869,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+湳</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -922,22 +903,19 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞(氵仲)</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㴌</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -961,23 +939,27 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無^</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+無^</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J11" s="4"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 아래 작은 ^ 꾸밈</t>
+        </is>
+      </c>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -1011,11 +993,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
+      <c r="I12" s="2"/>
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
@@ -1040,22 +1018,23 @@
       <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="J13" s="4"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 흘려 써 ×처럼 보임</t>
+        </is>
+      </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1079,23 +1058,23 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|汰</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰(氵黃·氵太)</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|湳</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15">
@@ -1131,7 +1110,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명</t>
+          <t xml:space="preserve">년</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1170,7 +1149,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">몸</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1199,18 +1178,18 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">학</t>
+          <t xml:space="preserve">되</t>
         </is>
       </c>
       <c r="J17" s="4"/>
@@ -1239,18 +1218,18 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
+㴌</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">운</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J18" s="4"/>
@@ -1277,23 +1256,27 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無^</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
-        </is>
-      </c>
-      <c r="J19" s="4"/>
+無^</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 아래 작은 ^ 꾸밈</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1329,7 +1312,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">을</t>
+          <t xml:space="preserve">서</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1393,13 +1376,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+△</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1439,7 +1422,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1479,7 +1462,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J24" s="4"/>
@@ -1508,17 +1491,18 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J25" s="4"/>
@@ -1545,26 +1529,22 @@
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청춘가</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제목이 이 칸에 적힘</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
+        </is>
+      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1590,15 +1570,19 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1625,15 +1609,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1671,7 +1659,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">불</t>
+          <t xml:space="preserve">학</t>
         </is>
       </c>
       <c r="J29" s="4"/>
@@ -1711,7 +1699,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오</t>
+          <t xml:space="preserve">문</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1740,18 +1728,18 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|南</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-南</t>
+姑</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오늘</t>
+          <t xml:space="preserve">을</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1790,7 +1778,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시</t>
+          <t xml:space="preserve">을</t>
         </is>
       </c>
       <c r="J32" s="4"/>
@@ -1862,11 +1850,7 @@
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+      <c r="I34" s="2"/>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1893,17 +1877,18 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다</t>
+          <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="J35" s="4"/>
@@ -1941,10 +1926,14 @@
 無</t>
         </is>
       </c>
-      <c r="I36" s="3"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">겹쳐 적힘, 확실치 않음</t>
+          <t xml:space="preserve">덧써서 흐림, 왼쪽에 ( 모양 획</t>
         </is>
       </c>
       <c r="K36" s="2"/>
@@ -1970,18 +1959,26 @@
       <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왼쪽 흐린 氵 획? 南일 수도</t>
+        </is>
+      </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -2005,23 +2002,23 @@
       <c r="F38" s="2">
         <v>1</v>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑|仲</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청</t>
-        </is>
-      </c>
-      <c r="J38" s="4"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 지운 글자(학?)</t>
+        </is>
+      </c>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -2045,22 +2042,22 @@
       <c r="F39" s="2">
         <v>1</v>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘</t>
-        </is>
-      </c>
-      <c r="J39" s="4"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 지운 글자</t>
+        </is>
+      </c>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -2084,18 +2081,22 @@
       <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="4"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 지운 글자</t>
+        </is>
+      </c>
       <c r="K40" s="2"/>
     </row>
     <row r="41">
@@ -2130,7 +2131,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I41" s="2"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닦</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2155,23 +2160,27 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無|南</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="J42" s="4"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 아/오?</t>
+        </is>
+      </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2207,7 +2216,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오늘</t>
+          <t xml:space="preserve">봅</t>
         </is>
       </c>
       <c r="J43" s="4"/>
@@ -2236,17 +2245,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥</t>
+          <t xml:space="preserve">시</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2286,7 +2295,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">안</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J45" s="4"/>
@@ -2313,22 +2322,26 @@
       <c r="F46" s="2">
         <v>3</v>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아안</t>
-        </is>
-      </c>
-      <c r="J46" s="4"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 리/다?</t>
+        </is>
+      </c>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2364,7 +2377,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">을</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J47" s="4"/>
@@ -2401,11 +2414,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
+      <c r="I48" s="2"/>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2432,12 +2441,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2467,18 +2477,18 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞</t>
+          <t xml:space="preserve">㴌|㳞</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">청</t>
         </is>
       </c>
       <c r="J50" s="4"/>
@@ -2505,22 +2515,26 @@
       <c r="F51" s="2">
         <v>1</v>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
-      <c r="J51" s="4"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">율명 아래 물결선</t>
+        </is>
+      </c>
       <c r="K51" s="2"/>
     </row>
     <row r="52">
@@ -2554,11 +2568,7 @@
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
-        </is>
-      </c>
+      <c r="I52" s="2"/>
       <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
@@ -2583,22 +2593,22 @@
       <c r="F53" s="2">
         <v>2</v>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
-        </is>
-      </c>
-      <c r="J53" s="4"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">율명 아래 물결선</t>
+        </is>
+      </c>
       <c r="K53" s="2"/>
     </row>
     <row r="54">
@@ -2624,12 +2634,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2657,18 +2667,22 @@
       <c r="F55" s="2">
         <v>2</v>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="4"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">율명 아래 물결선</t>
+        </is>
+      </c>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2694,17 +2708,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">라</t>
+          <t xml:space="preserve">홍</t>
         </is>
       </c>
       <c r="J56" s="4"/>
@@ -2733,16 +2747,20 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
+湳</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
       <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
@@ -2769,16 +2787,20 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아안</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2816,7 +2838,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">을</t>
         </is>
       </c>
       <c r="J59" s="4"/>
@@ -2853,7 +2875,11 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I60" s="2"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2880,12 +2906,13 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">·|△</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">·
+△</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2913,23 +2940,27 @@
       <c r="F62" s="2">
         <v>1</v>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|汰</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">덧</t>
-        </is>
-      </c>
-      <c r="J62" s="4"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|湳</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 비/네?(네 자랑)</t>
+        </is>
+      </c>
       <c r="K62" s="2"/>
     </row>
     <row r="63">
@@ -2965,7 +2996,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">없</t>
+          <t xml:space="preserve">자</t>
         </is>
       </c>
       <c r="J63" s="4"/>
@@ -3004,7 +3035,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">는</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J64" s="4"/>
@@ -3033,18 +3064,18 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세</t>
+          <t xml:space="preserve">마</t>
         </is>
       </c>
       <c r="J65" s="4"/>
@@ -3073,20 +3104,16 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월</t>
-        </is>
-      </c>
+㴌</t>
+        </is>
+      </c>
+      <c r="I66" s="2"/>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -3160,7 +3187,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">라</t>
         </is>
       </c>
       <c r="J68" s="4"/>
@@ -3270,7 +3297,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J71" s="4"/>
@@ -3335,12 +3362,13 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3370,18 +3398,18 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
+㴌</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">백</t>
+          <t xml:space="preserve">덧</t>
         </is>
       </c>
       <c r="J74" s="4"/>
@@ -3420,7 +3448,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">밭</t>
+          <t xml:space="preserve">없</t>
         </is>
       </c>
       <c r="J75" s="4"/>
@@ -3459,7 +3487,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="J76" s="4"/>
@@ -3498,7 +3526,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">되</t>
+          <t xml:space="preserve">세</t>
         </is>
       </c>
       <c r="J77" s="4"/>
@@ -3525,27 +3553,23 @@
       <c r="F78" s="2">
         <v>2</v>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㒇|南</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㒇
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㒇(亻無)? 확실치 않음</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월</t>
+        </is>
+      </c>
+      <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
     <row r="79">
@@ -3580,11 +3604,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
-        </is>
-      </c>
+      <c r="I79" s="2"/>
       <c r="J79" s="4"/>
       <c r="K79" s="2"/>
     </row>
@@ -3621,7 +3641,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J80" s="4"/>
@@ -3650,19 +3670,15 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I81" s="2"/>
       <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
@@ -3697,11 +3713,7 @@
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+      <c r="I82" s="2"/>
       <c r="J82" s="4"/>
       <c r="K82" s="2"/>
     </row>
@@ -3728,17 +3740,18 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J83" s="4"/>
@@ -3765,19 +3778,23 @@
       <c r="F84" s="2">
         <v>4</v>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I84" s="2"/>
-      <c r="J84" s="4"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덧써서 흐림, 왼쪽에 ( 모양 획</t>
+        </is>
+      </c>
       <c r="K84" s="2"/>
     </row>
     <row r="85">
@@ -3814,7 +3831,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳(氵南)</t>
+          <t xml:space="preserve">왼쪽 흐린 氵 획? 南일 수도</t>
         </is>
       </c>
       <c r="K85" s="2"/>
@@ -3851,7 +3868,11 @@
 仲</t>
         </is>
       </c>
-      <c r="I86" s="2"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백</t>
+        </is>
+      </c>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3886,7 +3907,11 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I87" s="2"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발</t>
+        </is>
+      </c>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
@@ -3921,7 +3946,11 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I88" s="2"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
@@ -3957,7 +3986,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I89" s="2"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되</t>
+        </is>
+      </c>
       <c r="J89" s="4"/>
       <c r="K89" s="2"/>
     </row>
@@ -3982,23 +4015,23 @@
       <c r="F90" s="2">
         <v>2</v>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|南</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I90" s="3"/>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
+      <c r="J90" s="4"/>
       <c r="K90" s="2"/>
     </row>
     <row r="91">
@@ -4032,7 +4065,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I91" s="2"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
@@ -4059,13 +4096,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4217,13 +4253,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I96" s="2"/>
@@ -4253,13 +4288,13 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+△</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4296,7 +4331,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="55.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4319,7 +4354,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="55.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4327,98 +4362,104 @@
 仲</t>
         </is>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">덧</t>
         </is>
       </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청</t>
-        </is>
-      </c>
-      <c r="L3" s="23" t="inlineStr">
+      <c r="K3" s="24"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청
-춘
-가</t>
-        </is>
-      </c>
-      <c r="N3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="O3" s="30"/>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="55.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발</t>
+        </is>
+      </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밭</t>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
@@ -4426,74 +4467,78 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">없</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘</t>
-        </is>
-      </c>
+      <c r="K4" s="26"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="31"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">명</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">딸</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -4501,9 +4546,9 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -4511,45 +4556,45 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몸</t>
+        </is>
+      </c>
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">손</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="Q5" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4557,65 +4602,69 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">되</t>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
-        </is>
-      </c>
+      <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="29"/>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닦</t>
+        </is>
+      </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불</t>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">학</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="O6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">학</t>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -4623,80 +4672,80 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55.96" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㒇
-南</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">운</t>
+㴌</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -4704,521 +4753,521 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" ht="55.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
-        </is>
-      </c>
+      <c r="E8" s="27"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I8" s="32"/>
+      <c r="I8" s="28"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오
-늘</t>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봅</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無^</t>
+        </is>
+      </c>
+      <c r="O8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="Q8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55.96" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홍</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55.96" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오
-늘</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+湳</t>
+        </is>
+      </c>
+      <c r="Q10" s="25"/>
+    </row>
+    <row r="11" ht="55.96" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+안</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="Q11" s="27"/>
+    </row>
+    <row r="12" ht="55.96" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
-        </is>
-      </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="Q8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無^</t>
+        </is>
+      </c>
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-南</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-南</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">안</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
+    </row>
+    <row r="13" ht="55.96" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="Q10" s="31"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-안</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q11" s="34"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
-      <c r="P12" s="21" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="O13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" ht="55.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E14" s="34"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="32"/>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M14" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="M14" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="32" t="inlineStr">
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q14" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -546,10 +546,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -492,17 +492,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -619,7 +619,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -677,6 +677,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4087,586 +4131,586 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="21"/>
+      <c r="L3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="23"/>
+      <c r="L4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="25"/>
+      <c r="L5" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="Q5" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="21"/>
+      <c r="J6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="22"/>
+      <c r="H7" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="9" t="s">
+      <c r="I7" s="22"/>
+      <c r="J7" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="Q7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="25"/>
+      <c r="J8" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="Q8" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="7" t="s">
+      <c r="M10" s="22"/>
+      <c r="N10" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="22"/>
+      <c r="P10" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Q10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="Q10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="24"/>
+      <c r="H11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="7" t="s">
+      <c r="M11" s="24"/>
+      <c r="N11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="7" t="s">
+      <c r="O11" s="24"/>
+      <c r="P11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="Q11" s="13"/>
-    </row>
-    <row r="12" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="Q12" s="21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="23"/>
+      <c r="F13" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="9" t="s">
+      <c r="K13" s="22"/>
+      <c r="L13" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="25"/>
+      <c r="F14" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="9" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="Q14" s="14"/>
+      <c r="Q14" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4674,7 +4718,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/청춘가.xlsx
+++ b/sheets/민요/검수/청춘가.xlsx
@@ -4137,26 +4137,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>48</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>50</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>50</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>57</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>82</v>
       </c>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>102</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>104</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>107</v>
       </c>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="Q10" s="22"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>102</v>
       </c>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>104</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>80</v>
       </c>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Q13" s="22"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>69</v>
       </c>
@@ -4718,7 +4718,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
